--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486683_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486683_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7058</v>
+        <v>6.5126</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9139</v>
+        <v>2.9691</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7919</v>
+        <v>3.5436</v>
       </c>
       <c r="G2" t="n">
         <v>6.693</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2485</v>
+        <v>0.0554</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3314</v>
+        <v>-0.2763</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5799</v>
+        <v>0.3316</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0426</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2357</v>
+        <v>2.2851</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4813</v>
+        <v>0.6339</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2455</v>
+        <v>1.6513</v>
       </c>
       <c r="G3" t="n">
-        <v>3.447</v>
+        <v>1.4156</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7033</v>
+        <v>4.2684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7437</v>
+        <v>-2.8528</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4553</v>
+        <v>-0.1211</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6007</v>
+        <v>2.7521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8545</v>
+        <v>-2.8731</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9917</v>
+        <v>1.5367</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1025</v>
+        <v>1.5164</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1108</v>
+        <v>0.0203</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3169</v>
+        <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5724</v>
+        <v>-0.8136</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1579</v>
+        <v>-0.3176</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4145</v>
+        <v>-0.496</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1698</v>
+        <v>2.4554</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7989</v>
+        <v>3.9687</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.9687</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1885</v>
+        <v>1.8635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7855</v>
+        <v>2.6056</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4029</v>
+        <v>-0.7421</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4156</v>
+        <v>3.447</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2684</v>
+        <v>2.7033</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.8528</v>
+        <v>0.7437</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1211</v>
+        <v>2.4553</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7521</v>
+        <v>1.6007</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.8731</v>
+        <v>0.8545</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5367</v>
+        <v>0.9917</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5164</v>
+        <v>1.1025</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0203</v>
+        <v>-0.1108</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1239</v>
+        <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9102</v>
+        <v>0.2001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1659</v>
+        <v>0.2823</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7443</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4554</v>
+        <v>-2.1698</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9687</v>
+        <v>1.7989</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5133</v>
+        <v>-3.9687</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7003</v>
+        <v>1.6439</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0035</v>
+        <v>-0.2515</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6968</v>
+        <v>1.8954</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7906</v>
@@ -844,13 +844,13 @@
         <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2814</v>
+        <v>-0.3378</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6891</v>
+        <v>0.434</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9705</v>
+        <v>-0.7718</v>
       </c>
       <c r="V5" t="n">
         <v>1.2277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4202</v>
+        <v>0.554</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.973</v>
+        <v>-0.8144</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3932</v>
+        <v>1.3684</v>
       </c>
       <c r="G6" t="n">
         <v>1.0397</v>
@@ -922,13 +922,13 @@
         <v>2.51</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6509</v>
+        <v>-0.5171</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1036</v>
+        <v>-0.945</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4528</v>
+        <v>0.428</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5133</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. RYTZ</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.289</v>
+        <v>0.2137</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9247</v>
+        <v>0.5592</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0475</v>
+        <v>0.1901</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4137</v>
+        <v>0.1652</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3662</v>
+        <v>0.0249</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0407</v>
+        <v>0.9978</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.3037</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0068</v>
+        <v>-0.8077</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4137</v>
+        <v>-0.1385</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4069</v>
+        <v>-0.6692</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4137</v>
+        <v>-0.0344</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.2412</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4137</v>
+        <v>-0.2756</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6565</v>
+        <v>-0.3282</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>K. RYTZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3034</v>
+        <v>-0.0822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0421</v>
+        <v>-0.7179</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3456</v>
+        <v>0.6357</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1901</v>
+        <v>0.0475</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1652</v>
+        <v>0.4137</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0249</v>
+        <v>-0.3662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9978</v>
+        <v>0.0407</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3037</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8077</v>
+        <v>0.0068</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1385</v>
+        <v>0.4137</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6692</v>
+        <v>-0.4069</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5515</v>
+        <v>-0.2068</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2759</v>
+        <v>0.2068</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2756</v>
+        <v>-0.4137</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3282</v>
+        <v>0.6565</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6138</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MAÏGA</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2164</v>
+        <v>-1.65</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0617</v>
+        <v>-3.0185</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1547</v>
+        <v>1.3685</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0208</v>
+        <v>-1.4088</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2898</v>
+        <v>-0.7103</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.269</v>
+        <v>-0.6984</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0141</v>
+        <v>-0.9525</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0141</v>
+        <v>-0.6407</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.3118</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0068</v>
+        <v>-0.4563</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2758</v>
+        <v>-0.0697</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.269</v>
+        <v>-0.3866</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9654</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0441</v>
+        <v>0.4965</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1104</v>
+        <v>-0.0693</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.5658</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>A. MAÏGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.494</v>
+        <v>-2.1171</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.639</v>
+        <v>-1.0617</v>
       </c>
       <c r="F10" t="n">
-        <v>1.145</v>
+        <v>-1.0554</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4088</v>
+        <v>0.0208</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7103</v>
+        <v>0.2898</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6984</v>
+        <v>-0.269</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9525</v>
+        <v>0.0141</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6407</v>
+        <v>0.0141</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3118</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4563</v>
+        <v>0.0068</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0697</v>
+        <v>0.2758</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3866</v>
+        <v>-0.269</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3475</v>
+        <v>0.0552</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6898</v>
+        <v>-0.1104</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3423</v>
+        <v>0.1655</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6138</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.947699999999999</v>
+        <v>9.2235</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6278999999999999</v>
+        <v>0.9038000000000008</v>
       </c>
       <c r="F11" t="n">
-        <v>8.319700000000001</v>
+        <v>8.319799999999999</v>
       </c>
       <c r="G11" t="n">
         <v>10.6543</v>
@@ -1285,7 +1285,7 @@
         <v>-3.4811</v>
       </c>
       <c r="J11" t="n">
-        <v>8.766500000000001</v>
+        <v>8.766499999999999</v>
       </c>
       <c r="K11" t="n">
         <v>11.0379</v>
@@ -1303,7 +1303,7 @@
         <v>-1.2097</v>
       </c>
       <c r="P11" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.4464</v>
@@ -1312,22 +1312,22 @@
         <v>15.4462</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3784</v>
+        <v>-1.1025</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8299999999999998</v>
+        <v>-0.5543</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5484</v>
+        <v>-0.5483</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3282000000000002</v>
+        <v>-0.3282000000000003</v>
       </c>
       <c r="W11" t="n">
         <v>8.1378</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.465900000000001</v>
+        <v>-8.4659</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2968</v>
+        <v>2.2267</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2899</v>
+        <v>4.2557</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.993</v>
+        <v>-2.029</v>
       </c>
       <c r="G12" t="n">
         <v>2.4134</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7596</v>
+        <v>0.6894</v>
       </c>
       <c r="T12" t="n">
-        <v>1.406</v>
+        <v>0.3718</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3536</v>
+        <v>0.3177</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8415</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2025</v>
+        <v>1.9708</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8538</v>
+        <v>0.647</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3486</v>
+        <v>1.3238</v>
       </c>
       <c r="G13" t="n">
         <v>1.4137</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4798</v>
+        <v>0.2482</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3584</v>
+        <v>0.1515</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1215</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6565</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.675</v>
+        <v>1.1914</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1227</v>
+        <v>1.2188</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5523</v>
+        <v>-0.0274</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5676</v>
+        <v>-1.113</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0692</v>
+        <v>-1.1311</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6367</v>
+        <v>0.0181</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4979</v>
+        <v>0.2329</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.3865</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5674</v>
+        <v>-0.1536</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0697</v>
+        <v>-1.3459</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0003</v>
+        <v>-1.5176</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0693</v>
+        <v>0.1717</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0495</v>
+        <v>-0.0897</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5513</v>
+        <v>-0.0487</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5019</v>
+        <v>-0.041</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2277</v>
+        <v>0.6565</v>
       </c>
       <c r="W14" t="n">
         <v>1.2277</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3544</v>
+        <v>0.7702</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4948</v>
+        <v>0.0192</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1404</v>
+        <v>0.751</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.113</v>
+        <v>-1.5676</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1311</v>
+        <v>0.0692</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0181</v>
+        <v>-1.6367</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2329</v>
+        <v>-0.4979</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3865</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1536</v>
+        <v>-0.5674</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3459</v>
+        <v>-1.0697</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5176</v>
+        <v>-0.0003</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1717</v>
+        <v>-1.0693</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9308</v>
+        <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9268</v>
+        <v>0.1447</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.4479</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1541</v>
+        <v>-0.3032</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W15" t="n">
         <v>1.2277</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.673</v>
+        <v>-0.6482</v>
       </c>
       <c r="E16" t="n">
         <v>-1.0206</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3475</v>
+        <v>0.3724</v>
       </c>
       <c r="G16" t="n">
         <v>0.1379</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0386</v>
+        <v>-0.0138</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5451</v>
+        <v>-1.2792</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3743</v>
+        <v>-2.6503</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8292</v>
+        <v>1.3711</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7588</v>
@@ -1780,13 +1780,13 @@
         <v>2.1239</v>
       </c>
       <c r="S17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.3379</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0486</v>
+        <v>-0.3246</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1206</v>
+        <v>0.6625</v>
       </c>
       <c r="V17" t="n">
         <v>3.9687</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6536</v>
+        <v>-3.1391</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5015</v>
+        <v>-2.3981</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1521</v>
+        <v>-0.741</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3329</v>
@@ -1936,13 +1936,13 @@
         <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2595</v>
+        <v>0.255</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2212</v>
+        <v>-0.1178</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0383</v>
+        <v>0.3728</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4128</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7551</v>
+        <v>-3.3937</v>
       </c>
       <c r="E20" t="n">
         <v>-3.783</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0279</v>
+        <v>0.3893</v>
       </c>
       <c r="G20" t="n">
         <v>-6.5106</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0168</v>
+        <v>0.3446</v>
       </c>
       <c r="T20" t="n">
         <v>0.0547</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.2899</v>
       </c>
       <c r="V20" t="n">
         <v>1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2447</v>
+        <v>-4.3522</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2661</v>
+        <v>-3.473</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9786</v>
+        <v>-0.8792</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1219</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0936</v>
+        <v>-0.0139</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4411</v>
+        <v>0.2343</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3475</v>
+        <v>-0.2481</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5133</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.947799999999999</v>
+        <v>-8.2583</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.319900000000001</v>
+        <v>-8.319899999999997</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6280000000000001</v>
+        <v>0.06160000000000032</v>
       </c>
       <c r="G22" t="n">
         <v>-10.6543</v>
@@ -2170,13 +2170,13 @@
         <v>15.4463</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3782</v>
+        <v>2.0678</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5481</v>
+        <v>0.5482</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8301000000000001</v>
+        <v>1.5197</v>
       </c>
       <c r="V22" t="n">
         <v>0.3283000000000005</v>
